--- a/template.xlsx
+++ b/template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12465" tabRatio="711"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12465" tabRatio="711" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Makine Listesi" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="35">
   <si>
     <t>Cihaz Numarası</t>
   </si>
@@ -65,6 +65,72 @@
   <si>
     <t>Alarm Türü</t>
   </si>
+  <si>
+    <t>Kontak Kapandı</t>
+  </si>
+  <si>
+    <t>Kontak Açıldı</t>
+  </si>
+  <si>
+    <t>K12******97</t>
+  </si>
+  <si>
+    <t>K12******99</t>
+  </si>
+  <si>
+    <t>Sarıba********* Türkiye</t>
+  </si>
+  <si>
+    <t>Düzce *********Türkiye</t>
+  </si>
+  <si>
+    <t>Camili*********Türkiye</t>
+  </si>
+  <si>
+    <t>1****28</t>
+  </si>
+  <si>
+    <t>1****30</t>
+  </si>
+  <si>
+    <t>06. BÖLGE (ADANA) - 06ARAÇLAR, LİEBHERR - HS825</t>
+  </si>
+  <si>
+    <t>Pazartesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3dk 50sn</t>
+  </si>
+  <si>
+    <t>Cuma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2dk 19sn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4sa 30dk 3sn</t>
+  </si>
+  <si>
+    <t>Salı</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3sa 59dk 22sn</t>
+  </si>
+  <si>
+    <t>Çarşamba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  29dk 23sn</t>
+  </si>
+  <si>
+    <t>Perşembe</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5sa 30dk 56sn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5sa 36dk 13sn</t>
+  </si>
 </sst>
 </file>
 
@@ -76,7 +142,7 @@
     <numFmt numFmtId="166" formatCode="[$-41F]hh:mm:ss;@"/>
     <numFmt numFmtId="167" formatCode="[$-41F]d\.m\.yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -131,6 +197,14 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -155,10 +229,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -188,8 +263,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -705,126 +782,654 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.48586805555555601</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.426377314814815</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.42643518518518497</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.50366898148148098</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.54854166666666704</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.63449074074074097</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.64703703703703697</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45754</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.67172453703703705</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>45755</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.49473379629629599</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="5">
+        <v>45755</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.61996527777777799</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.38711805555555601</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45756</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.645358796296296</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.496921296296296</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.547835648148148</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.54793981481481502</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.54796296296296299</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.62868055555555602</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.63892361111111096</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.63908564814814794</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.63916666666666699</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="5">
+        <v>45757</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.67084490740740699</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="5">
+        <v>45758</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.49660879629629601</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="5">
+        <v>45758</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.57094907407407403</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="5">
+        <v>45758</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.67158564814814803</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D27" s="5"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D28" s="5"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D30" s="5"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D32" s="5"/>
       <c r="E32" s="6"/>
     </row>
@@ -15530,8 +16135,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H2926"/>
+  <hyperlinks>
+    <hyperlink ref="H25" r:id="rId1"/>
+    <hyperlink ref="H2:H24" r:id="rId2" display="Haritada Göster"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -15574,25 +16183,186 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E2" s="8"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="8">
+        <v>45754</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E3" s="8"/>
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="8">
+        <v>45758</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E4" s="8"/>
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8">
+        <v>45754</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E5" s="8"/>
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="8">
+        <v>45755</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E6" s="8"/>
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8">
+        <v>45756</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E7" s="8"/>
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8">
+        <v>45757</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E8" s="8"/>
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="8">
+        <v>45758</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E9" s="8"/>
